--- a/backend/pypacity/cable/cable_db.xlsx
+++ b/backend/pypacity/cable/cable_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E9B122-2DB3-473C-AFC8-594310EC0838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EB68F0-CF1D-4E7A-920B-568A622E0757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1260" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>Cstring</t>
   </si>
@@ -147,6 +145,66 @@
   </si>
   <si>
     <t>LA-280</t>
+  </si>
+  <si>
+    <t>HERON</t>
+  </si>
+  <si>
+    <t>22.96</t>
+  </si>
+  <si>
+    <t>3.60</t>
+  </si>
+  <si>
+    <t>623.00</t>
+  </si>
+  <si>
+    <t>147.00</t>
+  </si>
+  <si>
+    <t>LA-455</t>
+  </si>
+  <si>
+    <t>27.72</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>971.40</t>
+  </si>
+  <si>
+    <t>220.00</t>
+  </si>
+  <si>
+    <t>0.1122</t>
+  </si>
+  <si>
+    <t>0.1507</t>
+  </si>
+  <si>
+    <t>0.0675</t>
+  </si>
+  <si>
+    <t>0.0906</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>8.04</t>
+  </si>
+  <si>
+    <t>8.61</t>
+  </si>
+  <si>
+    <t>9.24</t>
+  </si>
+  <si>
+    <t>D1</t>
   </si>
 </sst>
 </file>
@@ -464,13 +522,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" customWidth="1"/>
+    <col min="4" max="4" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,43 +549,46 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -522,43 +596,46 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>25</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>75</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
       <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
         <v>3</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -566,40 +643,43 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>85</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>100</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
       <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -607,37 +687,128 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>85</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>100</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>85</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>85</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
